--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,14 +528,14 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -544,18 +544,36 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B4" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C4" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -572,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -616,10 +634,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -628,7 +646,30 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -643,12 +684,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -659,10 +701,15 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -675,9 +722,12 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="D2" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -688,23 +738,45 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="D3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>2</v>
+      <c r="D5" s="4" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -731,10 +803,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -745,7 +817,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="21" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
@@ -753,21 +825,21 @@
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="28" customWidth="1" min="32" max="32"/>
-    <col width="28" customWidth="1" min="33" max="33"/>
+    <col width="30" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
     <col width="19" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
-    <col width="21" customWidth="1" min="42" max="42"/>
+    <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
     <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="21" customWidth="1" min="47" max="47"/>
+    <col width="24" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
     <col width="18" customWidth="1" min="50" max="50"/>
@@ -1092,10 +1164,8 @@
           <t>machama maharjan</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9767968876</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9767968876</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -1130,10 +1200,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.736575236789317</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.73657523678932</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -1171,10 +1239,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH2" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH2" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI2" s="3" t="inlineStr">
         <is>
@@ -1193,25 +1259,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>L29-2</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>27.736575236789317</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>27.73657523678932</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : stb box faulty   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">
@@ -1253,7 +1315,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>18 Oct 2026 10:41 AM</t>
+          <t>18 Oct 2026 10:37 AM</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1279,22 +1341,22 @@
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Case : stb box faulty   has been updated by Sunil Chaudhary</t>
+          <t>Case : router damage issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>stb box faulty</t>
+          <t>router damage issue</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>TKT1373949</t>
+          <t>TKT1373790</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>machama maharjan</t>
+          <t>Babu Raja Maharjan</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -1302,20 +1364,14 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
+      <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>machama maharjan</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9767968876</t>
-        </is>
+          <t>Babu Raja Maharjan</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>9802243292</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1325,24 +1381,24 @@
       <c r="Q3" s="3" t="inlineStr"/>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>17 Oct 2026 09:29:55 PM</t>
+          <t>17 Oct 2026 04:53:20 PM</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>KLK9767968876</t>
+          <t>9802243292</t>
         </is>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
-          <t>17 Oct 2026 09:25:44 PM</t>
+          <t>17 Oct 2026 04:49:27 PM</t>
         </is>
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>18 Oct 2026 10:41:52 AM</t>
+          <t>18 Oct 2026 10:37:10 AM</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
@@ -1350,10 +1406,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>27.736575236789317</t>
-        </is>
+      <c r="Y3" s="3" t="n">
+        <v>27.74316</v>
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
@@ -1362,7 +1416,7 @@
       </c>
       <c r="AA3" s="3" t="inlineStr">
         <is>
-          <t>Layer 2-CG Group</t>
+          <t>Layer 1-</t>
         </is>
       </c>
       <c r="AB3" s="3" t="inlineStr">
@@ -1372,40 +1426,36 @@
       </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AD3" s="3" t="inlineStr"/>
       <c r="AE3" s="3" t="inlineStr">
         <is>
-          <t>27.736575236789317, 27.736575236789317, Kathmandu, Nepal, Nepal</t>
+          <t>basundhara chauki near Southwestern State College, Bagmati, Central, Nepal</t>
         </is>
       </c>
       <c r="AF3" s="3" t="inlineStr">
         <is>
-          <t>9767968876@gmail.com</t>
+          <t>baburajmaharjan@gmail.com</t>
         </is>
       </c>
       <c r="AG3" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
-        </is>
-      </c>
-      <c r="AH3" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr"/>
       <c r="AI3" s="3" t="inlineStr">
         <is>
-          <t>00:00 hour</t>
+          <t>03:11 hour</t>
         </is>
       </c>
       <c r="AJ3" s="3" t="inlineStr"/>
       <c r="AK3" s="3" t="inlineStr"/>
       <c r="AL3" s="3" t="inlineStr">
         <is>
-          <t>Dinesh Rawat</t>
+          <t>Aakash Shah</t>
         </is>
       </c>
       <c r="AM3" s="3" t="inlineStr">
@@ -1413,35 +1463,31 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
-          <t>L29-2</t>
-        </is>
-      </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>27.736575236789317</t>
-        </is>
+          <t>2,7</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="n">
+        <v>85.33889000000001</v>
       </c>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : stb box faulty   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
         <is>
-          <t>13h 11m</t>
+          <t>17h 43m</t>
         </is>
       </c>
       <c r="AT3" s="3" t="inlineStr">
         <is>
-          <t>13h 16m</t>
+          <t>17h 47m</t>
         </is>
       </c>
       <c r="AU3" s="3" t="inlineStr">
@@ -1451,7 +1497,7 @@
       </c>
       <c r="AV3" s="3" t="inlineStr">
         <is>
-          <t>Case : stb box faulty   has been updated by Sunil Chaudhary</t>
+          <t>Case : router damage issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="AW3" s="3" t="inlineStr">
@@ -1473,7 +1519,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>18 Oct 2026 10:37 AM</t>
+          <t>18 Oct 2026 10:36 AM</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1522,20 +1568,14 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Babu Raja Maharjan</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9802243292</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9802243292</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1570,10 +1610,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.74316</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.74316</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1629,25 +1667,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>2,7</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.33889</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.33889000000001</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : router damage issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
@@ -1684,22 +1718,22 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>18 Oct 2026 10:36 AM</t>
+          <t>18 Oct 2026 10:59 AM</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -1715,70 +1749,70 @@
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Case : router damage issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : iptv issue   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>router damage issue</t>
+          <t>iptv issue</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>TKT1373790</t>
+          <t>TKT1373564</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Babu Raja Maharjan</t>
+          <t>Dharma Ratna shakya</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>Babu Raja Maharjan</t>
+          <t>Dharma Ratna shakya</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>9802243292</t>
+          <t>9841593447</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr"/>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>17 Oct 2026 04:53:20 PM</t>
+          <t>18 Oct 2026 10:59:14 AM</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>9802243292</t>
+          <t>9841593447</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>17 Oct 2026 04:49:27 PM</t>
+          <t>17 Oct 2026 11:56:46 AM</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>18 Oct 2026 10:37:10 AM</t>
+          <t>18 Oct 2026 10:59:14 AM</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
@@ -1786,114 +1820,102 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.74316</t>
-        </is>
-      </c>
+      <c r="Y5" s="3" t="inlineStr"/>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
-          <t>Layer 1-</t>
+          <t>Layer 1-User</t>
         </is>
       </c>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>Laxman Koirala</t>
+          <t>L1  Support</t>
         </is>
       </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AD5" s="3" t="inlineStr"/>
       <c r="AE5" s="3" t="inlineStr">
         <is>
-          <t>basundhara chauki near Southwestern State College, Bagmati, Central, Nepal</t>
-        </is>
-      </c>
-      <c r="AF5" s="3" t="inlineStr">
-        <is>
-          <t>baburajmaharjan@gmail.com</t>
-        </is>
-      </c>
+          <t>27.669819, 85.326742, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr"/>
       <c r="AG5" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="AH5" s="3" t="inlineStr"/>
       <c r="AI5" s="3" t="inlineStr">
         <is>
-          <t>03:11 hour</t>
+          <t>08:04 hour</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="inlineStr"/>
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" s="3" t="inlineStr">
         <is>
-          <t>Aakash Shah</t>
+          <t>Nirmaya Mukhiya</t>
         </is>
       </c>
       <c r="AM5" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="AN5" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
-          <t>2,7</t>
-        </is>
-      </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.33889</t>
-        </is>
-      </c>
+          <t>L107-5</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr"/>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : router damage issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : iptv issue   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
         <is>
-          <t>17h 43m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="AT5" s="3" t="inlineStr">
         <is>
-          <t>17h 47m</t>
+          <t>23h 2m</t>
         </is>
       </c>
       <c r="AU5" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="AV5" s="3" t="inlineStr">
         <is>
-          <t>Case : router damage issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : iptv issue   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="AW5" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Issue</t>
         </is>
       </c>
       <c r="AX5" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
@@ -836,7 +836,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1782,10 +1782,8 @@
           <t>Dharma Ratna shakya</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9841593447</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9841593447</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1871,10 +1869,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
@@ -1885,7 +1881,7 @@
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -646,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,30 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>16.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -684,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -718,23 +741,23 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -750,33 +773,49 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>3</v>
+      <c r="C6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -790,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX5"/>
+  <dimension ref="A1:AX7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -836,10 +875,10 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="32" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
     <col width="18" customWidth="1" min="50" max="50"/>
@@ -1915,6 +1954,422 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 11:35 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373226</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Mainali</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Mainali</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9851330557</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 08:13:58 PM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9851330557</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 08:13:58 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 11:35:33 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>27.75457483862807, 85.32602632379277, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>L36-1</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>1d 15h 21m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>1d 15h 21m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 11:32 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372734</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Ram Dhayal Mahato</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Ram Dhayal Mahato</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9841455936</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 12:11:07 PM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9841455936</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 12:11:07 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 11:32:58 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>27.73283</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Chundevi Temple Kathmandu 27.73548, 85.33781, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>ramdayal202011@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>17:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>L43-5</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>85.33553</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 21m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 21m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>5</v>
-      </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -680,19 +680,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -745,13 +745,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>4</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -829,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX7"/>
+  <dimension ref="A1:AX8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2011,20 +2011,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="3" t="inlineStr">
         <is>
           <t>Prabin Mainali</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9851330557</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9851330557</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -2106,10 +2100,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
@@ -2120,7 +2112,7 @@
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
@@ -2221,10 +2213,8 @@
           <t>Ram Dhayal Mahato</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9841455936</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9841455936</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -2259,10 +2249,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>27.73283</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>27.73283</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -2318,47 +2306,43 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>L43-5</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>85.33553</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>85.33553000000001</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 21m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 21m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS7" s="3" t="inlineStr">
-        <is>
-          <t>1d 23h 21m</t>
-        </is>
-      </c>
-      <c r="AT7" s="3" t="inlineStr">
-        <is>
-          <t>1d 23h 21m</t>
-        </is>
-      </c>
-      <c r="AU7" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV7" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW7" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -2367,6 +2351,222 @@
       <c r="AX7" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 11:52 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373582</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Manohar Budathoki</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Manohar Budathoki</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9851170865</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 11:52:47 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9851170865</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 12:18:53 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 11:52:47 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.67018</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur, Kumaripati, Korean Shop, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>sudobhsb81@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>07:42 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>3,11</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.32149</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>23h 33m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,14 +528,14 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Rajesh Maharjan</t>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -546,36 +546,54 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>85.7%</t>
+      <c r="B5" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>91.7%</t>
         </is>
       </c>
     </row>
@@ -646,7 +664,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -657,10 +675,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -669,7 +687,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -680,19 +698,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
     </row>
@@ -707,13 +725,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -724,15 +743,20 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -748,10 +772,13 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="n">
         <v>3</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -761,61 +788,111 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="6" t="n">
-        <v>1</v>
+      <c r="E3" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>6</v>
+      <c r="D8" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -829,23 +906,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX8"/>
+  <dimension ref="A1:AX13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -863,14 +940,14 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="28" customWidth="1" min="32" max="32"/>
-    <col width="30" customWidth="1" min="33" max="33"/>
+    <col width="30" customWidth="1" min="32" max="32"/>
+    <col width="38" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="18" customWidth="1" min="38" max="38"/>
-    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
@@ -881,7 +958,7 @@
     <col width="32" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
-    <col width="18" customWidth="1" min="50" max="50"/>
+    <col width="20" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2421,10 +2498,8 @@
           <t>Manohar Budathoki</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9851170865</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9851170865</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2459,10 +2534,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.67018</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.67018</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2518,55 +2591,1119 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>3,11</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.32149</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.32149</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>23h 33m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS8" s="3" t="inlineStr">
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:17 PM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372411</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Subarna Lal Maharjan</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Subarna Lal Maharjan</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9851160664</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 08:57:33 AM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9851160664</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 08:57:33 AM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:17:22 PM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.72614</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Ranibari, Near Dakshinkali Cold Store, Kathmandu, Bagmati, Central, Nepal, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr"/>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>20:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>L18-7</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.3177</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 19m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 19m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:14 PM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>iptv not working</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372612</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Arjyal</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Arjyal</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9841380245</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:14:55 PM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>CHB9841380245</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 10:50:43 AM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:14:55 PM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr"/>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Om Hospital &amp; Research Centre Pvt. Ltd. - Private hospital ?????? ??? Kathmandu 44602, Kathmandu, Ne</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>test@test.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-No internet connection in STB</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>19:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>L30-3</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT8" s="3" t="inlineStr">
-        <is>
-          <t>23h 33m</t>
-        </is>
-      </c>
-      <c r="AU8" s="3" t="inlineStr">
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 24m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV8" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW8" s="3" t="inlineStr">
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:12 PM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Exchange my IPTV Device   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Exchange my IPTV Device</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373603</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Janak Adhikari</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Janak Adhikari</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9843693628</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:12:49 PM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9843693628</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 12:40:44 PM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:12:49 PM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>27.71839</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>hadi gaun marga, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>janak.adhikari211@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>07:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr"/>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>L5-8</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>85.33509</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Exchange my IPTV Device   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>23h 32m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Exchange my IPTV Device   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:11 PM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373459</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Palpa Paudel</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Palpa Paudel</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9841264468</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:11:45 PM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9841264468</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 10:06:06 AM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:11:45 PM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.71391</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Shanti park, Partitar, Kathmandu 44600, ???????? 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>palpa.paudel@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>09:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>L29-4</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.36242</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 5m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX8" s="3" t="inlineStr">
-        <is>
-          <t>Rajesh Maharjan</t>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:10 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>IPTV ISSUE</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373364</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Rupa lama</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Rupa lama</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9813496508</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:10:31 PM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9813496508</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 08:11:35 AM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:10:31 PM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>27.716652</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>mulpani cricket ground , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr"/>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>10:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Sanam Sadar</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>L34-4</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>85.392235</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 58m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
@@ -952,7 +952,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2706,10 +2706,8 @@
           <t>Subarna Lal Maharjan</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9851160664</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9851160664</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2744,10 +2742,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>27.72614</t>
-        </is>
+      <c r="Y9" s="3" t="n">
+        <v>27.72614</v>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
@@ -2799,25 +2795,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>L18-7</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.3177</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.3177</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -2918,10 +2910,8 @@
           <t>Rajesh Arjyal</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9841380245</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9841380245</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2993,10 +2983,8 @@
           <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
-      <c r="AH10" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH10" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI10" s="3" t="inlineStr">
         <is>
@@ -3015,10 +3003,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
@@ -3029,7 +3015,7 @@
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -3130,10 +3116,8 @@
           <t>Janak Adhikari</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9843693628</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9843693628</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -3168,10 +3152,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>27.71839</t>
-        </is>
+      <c r="Y11" s="3" t="n">
+        <v>27.71839</v>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -3227,25 +3209,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>L5-8</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>85.33509</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>85.33508999999999</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : Exchange my IPTV Device   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
@@ -3346,10 +3324,8 @@
           <t>Palpa Paudel</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9841264468</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9841264468</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -3384,10 +3360,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.71391</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.71391</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -3443,25 +3417,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>L29-4</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.36242</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.36242</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
@@ -3562,10 +3532,8 @@
           <t>Rupa lama</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9813496508</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9813496508</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3600,10 +3568,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>27.716652</t>
-        </is>
+      <c r="Y13" s="3" t="n">
+        <v>27.716652</v>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
@@ -3655,25 +3621,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>L34-4</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>85.392235</t>
-        </is>
+      <c r="AP13" s="3" t="n">
+        <v>85.392235</v>
       </c>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>11</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>84.6%</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.8%</t>
         </is>
       </c>
     </row>
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>46.2%</t>
         </is>
       </c>
     </row>
@@ -775,10 +775,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -889,10 +889,10 @@
         <v>2</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -906,7 +906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX13"/>
+  <dimension ref="A1:AX14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -952,7 +952,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3669,6 +3669,218 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 2:57 PM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372925</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Poonam Thapa</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Poonam Thapa</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9848029115</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:51:48 PM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9848029115</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:51:48 PM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 02:57:36 PM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.74773</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Ganesh Mandir,P8XH+4PF, Tokha,Fisal Tole, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>poonamthapa7777@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>L7-8</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.32958</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>2d 5m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>2d 5m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
@@ -952,7 +952,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3736,10 +3736,8 @@
           <t>Poonam Thapa</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9848029115</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9848029115</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3774,10 +3772,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>27.74773</t>
-        </is>
+      <c r="Y14" s="3" t="n">
+        <v>27.74773</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
@@ -3829,25 +3825,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>L7-8</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.32958</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.32958000000001</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>11</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>21.4%</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -822,17 +822,17 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>1</v>
@@ -841,17 +841,17 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Blank TV Display</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>1</v>
@@ -860,14 +860,14 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>SKYCOM-Blank TV Display</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
@@ -877,22 +877,41 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" s="4" t="n">
+      <c r="C9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E8" s="4" t="n">
-        <v>12</v>
+      <c r="E9" s="4" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -906,7 +925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX14"/>
+  <dimension ref="A1:AX15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3873,6 +3892,114 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 3:23 PM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV not working   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr"/>
+      <c r="V15" s="3" t="inlineStr"/>
+      <c r="W15" s="3" t="inlineStr"/>
+      <c r="X15" s="3" t="inlineStr"/>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr"/>
+      <c r="AA15" s="3" t="inlineStr"/>
+      <c r="AB15" s="3" t="inlineStr"/>
+      <c r="AC15" s="3" t="inlineStr"/>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr"/>
+      <c r="AF15" s="3" t="inlineStr"/>
+      <c r="AG15" s="3" t="inlineStr"/>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr"/>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr"/>
+      <c r="AM15" s="3" t="inlineStr"/>
+      <c r="AN15" s="3" t="inlineStr"/>
+      <c r="AO15" s="3" t="inlineStr"/>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV not working   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX15" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>81.2%</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -775,10 +775,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -908,10 +908,10 @@
         <v>3</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -925,7 +925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX15"/>
+  <dimension ref="A1:AX17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -971,7 +971,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4000,6 +4000,438 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 3:36 PM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372989</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Tejendra Regmi</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Tejendra Regmi</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9851179207</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:53:54 PM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9851179207</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:53:54 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 03:36:06 PM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>27.72692</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Sarkari Dhara,P8G7+JMW, Samakhusi Marg, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>14:07 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>L22-5</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 42m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 42m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 3:35 PM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372989</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Tejendra Regmi</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Tejendra Regmi</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9851179207</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:53:54 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9851179207</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:53:54 PM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 03:36:06 PM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>27.72692</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Sarkari Dhara,P8G7+JMW, Samakhusi Marg, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>14:07 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>L22-5</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 42m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 42m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
@@ -971,7 +971,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4067,10 +4067,8 @@
           <t>Tejendra Regmi</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9851179207</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9851179207</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -4105,10 +4103,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>27.72692</t>
-        </is>
+      <c r="Y16" s="3" t="n">
+        <v>27.72692</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
@@ -4164,25 +4160,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>L22-5</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -4283,10 +4275,8 @@
           <t>Tejendra Regmi</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9851179207</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9851179207</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -4321,10 +4311,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>27.72692</t>
-        </is>
+      <c r="Y17" s="3" t="n">
+        <v>27.72692</v>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
@@ -4380,25 +4368,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
           <t>L22-5</t>
         </is>
       </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP17" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>82.4%</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
     </row>
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
     </row>
@@ -772,13 +772,13 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>5</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -905,13 +905,13 @@
         <v>4</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -925,7 +925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX17"/>
+  <dimension ref="A1:AX18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -971,7 +971,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4416,6 +4416,214 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 4:18 PM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374134</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Baburaja Maharjan</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Baburaja Maharjan</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9801855562</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 04:18:08 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>LTP9801855562</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 10:23:07 AM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 04:18:08 PM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr"/>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Avens English Boarding School Avens English Boarding School - School 44600 Ring Rd Lalitpur 44700, K</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>9841567276@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>2,1</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr"/>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>5h 55m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>7</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>14</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>73.7%</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>15.8%</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>21.1%</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>47.4%</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX18"/>
+  <dimension ref="A1:AX20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -971,7 +971,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4483,10 +4483,8 @@
           <t>Baburaja Maharjan</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9801855562</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9801855562</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4576,10 +4574,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
@@ -4590,29 +4586,29 @@
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>5h 55m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS18" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT18" s="3" t="inlineStr">
-        <is>
-          <t>5h 55m</t>
-        </is>
-      </c>
-      <c r="AU18" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV18" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="AW18" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -4621,6 +4617,222 @@
       <c r="AX18" s="3" t="inlineStr">
         <is>
           <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 4:40 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr"/>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr"/>
+      <c r="V19" s="3" t="inlineStr"/>
+      <c r="W19" s="3" t="inlineStr"/>
+      <c r="X19" s="3" t="inlineStr"/>
+      <c r="Y19" s="3" t="inlineStr"/>
+      <c r="Z19" s="3" t="inlineStr"/>
+      <c r="AA19" s="3" t="inlineStr"/>
+      <c r="AB19" s="3" t="inlineStr"/>
+      <c r="AC19" s="3" t="inlineStr"/>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr"/>
+      <c r="AF19" s="3" t="inlineStr"/>
+      <c r="AG19" s="3" t="inlineStr"/>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr"/>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr"/>
+      <c r="AM19" s="3" t="inlineStr"/>
+      <c r="AN19" s="3" t="inlineStr"/>
+      <c r="AO19" s="3" t="inlineStr"/>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 4:39 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr"/>
+      <c r="N20" s="3" t="inlineStr"/>
+      <c r="O20" s="3" t="inlineStr"/>
+      <c r="P20" s="3" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr"/>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr"/>
+      <c r="V20" s="3" t="inlineStr"/>
+      <c r="W20" s="3" t="inlineStr"/>
+      <c r="X20" s="3" t="inlineStr"/>
+      <c r="Y20" s="3" t="inlineStr"/>
+      <c r="Z20" s="3" t="inlineStr"/>
+      <c r="AA20" s="3" t="inlineStr"/>
+      <c r="AB20" s="3" t="inlineStr"/>
+      <c r="AC20" s="3" t="inlineStr"/>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr"/>
+      <c r="AF20" s="3" t="inlineStr"/>
+      <c r="AG20" s="3" t="inlineStr"/>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr"/>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr"/>
+      <c r="AM20" s="3" t="inlineStr"/>
+      <c r="AN20" s="3" t="inlineStr"/>
+      <c r="AO20" s="3" t="inlineStr"/>
+      <c r="AP20" s="3" t="inlineStr"/>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>15.0%</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>2</v>
@@ -778,7 +778,7 @@
         <v>5</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>4</v>
@@ -911,7 +911,7 @@
         <v>7</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -925,7 +925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX20"/>
+  <dimension ref="A1:AX21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -971,7 +971,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4836,6 +4836,218 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 4:53 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371605</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Ramita Pujari</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Ramita Pujari</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9818579073</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 04:53:14 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9818579073</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 11:27:33 AM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 04:53:14 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>27.711797</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>Namrata Stationery &amp; Gift Center, P863+MPJ, Purano Dhalko Marg, Kathmandu 44600, Bagmati, Central, N</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr"/>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>04:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>2,14</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr">
+        <is>
+          <t>85.304165</t>
+        </is>
+      </c>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>3d 5h 25m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
@@ -971,7 +971,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4903,10 +4903,8 @@
           <t>Ramita Pujari</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9818579073</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9818579073</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -4941,10 +4939,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y21" s="3" t="inlineStr">
-        <is>
-          <t>27.711797</t>
-        </is>
+      <c r="Y21" s="3" t="n">
+        <v>27.711797</v>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
@@ -4996,25 +4992,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>2,14</t>
         </is>
       </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>85.304165</t>
-        </is>
+      <c r="AP21" s="3" t="n">
+        <v>85.304165</v>
       </c>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>76.2%</t>
         </is>
       </c>
     </row>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>19.0%</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>19.0%</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.6%</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -803,7 +803,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -813,10 +813,10 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -841,17 +841,17 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>4</v>
@@ -911,7 +911,7 @@
         <v>7</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -925,7 +925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX21"/>
+  <dimension ref="A1:AX22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -971,7 +971,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -5040,6 +5040,218 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 5:31 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : ONT replacement  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>ONT replacement</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373659</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Lal Bahadur Shrestha</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Lal Bahadur Shrestha</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9802092474</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 05:31:31 PM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9802092474</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 01:56:51 PM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 05:31:31 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>27.72108</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Near Khusibun Judo Hall, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr"/>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>06:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>1,16</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>85.305</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : ONT replacement  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 34m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : ONT replacement  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Oct_2026.xlsx
@@ -971,7 +971,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -5107,10 +5107,8 @@
           <t>Lal Bahadur Shrestha</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9802092474</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9802092474</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -5145,10 +5143,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t>27.72108</t>
-        </is>
+      <c r="Y22" s="3" t="n">
+        <v>27.72108</v>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
@@ -5200,25 +5196,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>1,16</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>85.305</t>
-        </is>
+      <c r="AP22" s="3" t="n">
+        <v>85.30500000000001</v>
       </c>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : ONT replacement  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
